--- a/artfynd/A 51688-2021 artfynd.xlsx
+++ b/artfynd/A 51688-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1635,6 +1635,131 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114700453</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97528</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tarmlången, norr om, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>617090</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6651194</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>C-Upp-0966</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>15 bladrosetter i två kloner.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51688-2021 artfynd.xlsx
+++ b/artfynd/A 51688-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51688-2021 artfynd.xlsx
+++ b/artfynd/A 51688-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1760,6 +1760,117 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118931156</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90511</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tarmlången, norr om, Morgongåva-Östfora, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>616900</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6651133</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Återfunnen efter avverkning</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51688-2021 artfynd.xlsx
+++ b/artfynd/A 51688-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1637,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114700453</v>
+        <v>118931156</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
+        <v>90513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,50 +1649,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tarmlången, norr om, Upl</t>
+          <t>Tarmlången, norr om, Morgongåva-Östfora, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>617090</v>
+        <v>616900</v>
       </c>
       <c r="R10" t="n">
-        <v>6651194</v>
+        <v>6651133</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1714,24 +1708,19 @@
           <t>Järlåsa</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>C-Upp-0966</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>15 bladrosetter i två kloner.</t>
+          <t>Återfunnen efter avverkning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,136 +1729,22 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>118931156</v>
-      </c>
-      <c r="B11" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tarmlången, norr om, Morgongåva-Östfora, Upl</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>616900</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6651133</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Järlåsa</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Återfunnen efter avverkning</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
           <t>Vilhelm Kroon</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
